--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848551</v>
+        <v>124848578</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457116</v>
+        <v>456928</v>
       </c>
       <c r="R2" t="n">
-        <v>6925215</v>
+        <v>6925545</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848584</v>
+        <v>124848560</v>
       </c>
       <c r="B3" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456896</v>
+        <v>457173</v>
       </c>
       <c r="R3" t="n">
-        <v>6925616</v>
+        <v>6925356</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848576</v>
+        <v>124848554</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457051</v>
+        <v>456857</v>
       </c>
       <c r="R4" t="n">
-        <v>6925537</v>
+        <v>6925333</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,13 +962,17 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -987,7 +991,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848578</v>
+        <v>124848577</v>
       </c>
       <c r="B5" t="n">
         <v>91008</v>
@@ -1027,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456928</v>
+        <v>457050</v>
       </c>
       <c r="R5" t="n">
-        <v>6925545</v>
+        <v>6925282</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848556</v>
+        <v>124848583</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1129,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456917</v>
+        <v>456916</v>
       </c>
       <c r="R6" t="n">
-        <v>6925573</v>
+        <v>6925584</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848545</v>
+        <v>124848549</v>
       </c>
       <c r="B7" t="n">
-        <v>78905</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>967</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1236,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456823</v>
+        <v>457151</v>
       </c>
       <c r="R7" t="n">
-        <v>6925376</v>
+        <v>6925474</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848554</v>
+        <v>124848576</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1338,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456857</v>
+        <v>457051</v>
       </c>
       <c r="R8" t="n">
-        <v>6925333</v>
+        <v>6925537</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1376,17 +1375,13 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1405,10 +1400,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848579</v>
+        <v>124848546</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,21 +1416,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1445,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456957</v>
+        <v>457165</v>
       </c>
       <c r="R9" t="n">
-        <v>6925524</v>
+        <v>6925267</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,11 +1476,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1512,10 +1502,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848573</v>
+        <v>124848556</v>
       </c>
       <c r="B10" t="n">
-        <v>78889</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1528,21 +1518,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1552,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457004</v>
+        <v>456917</v>
       </c>
       <c r="R10" t="n">
-        <v>6925576</v>
+        <v>6925573</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,6 +1578,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1614,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848557</v>
+        <v>124848548</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,21 +1625,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1654,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457156</v>
+        <v>457064</v>
       </c>
       <c r="R11" t="n">
-        <v>6925470</v>
+        <v>6925274</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,11 +1685,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1721,10 +1711,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848560</v>
+        <v>124848547</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1737,21 +1727,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1761,10 +1751,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457173</v>
+        <v>456911</v>
       </c>
       <c r="R12" t="n">
-        <v>6925356</v>
+        <v>6925161</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,11 +1787,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1828,10 +1813,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848549</v>
+        <v>124848579</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1844,21 +1829,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1868,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457151</v>
+        <v>456957</v>
       </c>
       <c r="R13" t="n">
-        <v>6925474</v>
+        <v>6925524</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,6 +1889,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1930,10 +1920,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848547</v>
+        <v>124848551</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1946,21 +1936,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1970,10 +1960,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456911</v>
+        <v>457116</v>
       </c>
       <c r="R14" t="n">
-        <v>6925161</v>
+        <v>6925215</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,6 +1996,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2032,10 +2027,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848546</v>
+        <v>124848558</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2048,21 +2043,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2072,10 +2067,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457165</v>
+        <v>457197</v>
       </c>
       <c r="R15" t="n">
-        <v>6925267</v>
+        <v>6925420</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,6 +2103,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,10 +2241,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124848577</v>
+        <v>124848545</v>
       </c>
       <c r="B17" t="n">
-        <v>91008</v>
+        <v>78905</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2257,21 +2257,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>967</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457050</v>
+        <v>456823</v>
       </c>
       <c r="R17" t="n">
-        <v>6925282</v>
+        <v>6925376</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2343,10 +2343,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124848583</v>
+        <v>124848553</v>
       </c>
       <c r="B18" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2359,21 +2359,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2383,10 +2383,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456916</v>
+        <v>456909</v>
       </c>
       <c r="R18" t="n">
-        <v>6925584</v>
+        <v>6925153</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,6 +2419,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2445,10 +2450,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124848548</v>
+        <v>124848557</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2461,21 +2466,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2485,10 +2490,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457064</v>
+        <v>457156</v>
       </c>
       <c r="R19" t="n">
-        <v>6925274</v>
+        <v>6925470</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,6 +2526,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2547,10 +2557,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124848553</v>
+        <v>124848584</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2563,21 +2573,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2587,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456909</v>
+        <v>456896</v>
       </c>
       <c r="R20" t="n">
-        <v>6925153</v>
+        <v>6925616</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2623,11 +2633,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2654,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124848558</v>
+        <v>124848573</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2670,21 +2675,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2694,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457197</v>
+        <v>457004</v>
       </c>
       <c r="R21" t="n">
-        <v>6925420</v>
+        <v>6925576</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,11 +2735,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848578</v>
+        <v>124848560</v>
       </c>
       <c r="B2" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456928</v>
+        <v>457173</v>
       </c>
       <c r="R2" t="n">
-        <v>6925545</v>
+        <v>6925356</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848560</v>
+        <v>124848554</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457173</v>
+        <v>456857</v>
       </c>
       <c r="R3" t="n">
-        <v>6925356</v>
+        <v>6925333</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack färska på tall</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848554</v>
+        <v>124848578</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456857</v>
+        <v>456928</v>
       </c>
       <c r="R4" t="n">
-        <v>6925333</v>
+        <v>6925545</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2241,10 +2241,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124848545</v>
+        <v>124848557</v>
       </c>
       <c r="B17" t="n">
-        <v>78905</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2257,21 +2257,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>967</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456823</v>
+        <v>457156</v>
       </c>
       <c r="R17" t="n">
-        <v>6925376</v>
+        <v>6925470</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,6 +2317,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2343,10 +2348,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124848553</v>
+        <v>124848545</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>78905</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2359,21 +2364,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>967</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2383,10 +2388,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456909</v>
+        <v>456823</v>
       </c>
       <c r="R18" t="n">
-        <v>6925153</v>
+        <v>6925376</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,11 +2424,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2450,7 +2450,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124848557</v>
+        <v>124848553</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457156</v>
+        <v>456909</v>
       </c>
       <c r="R19" t="n">
-        <v>6925470</v>
+        <v>6925153</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848560</v>
+        <v>124848548</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457173</v>
+        <v>457064</v>
       </c>
       <c r="R2" t="n">
-        <v>6925356</v>
+        <v>6925274</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848554</v>
+        <v>124848546</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456857</v>
+        <v>457165</v>
       </c>
       <c r="R3" t="n">
-        <v>6925333</v>
+        <v>6925267</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848578</v>
+        <v>124848554</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456928</v>
+        <v>456857</v>
       </c>
       <c r="R4" t="n">
-        <v>6925545</v>
+        <v>6925333</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848577</v>
+        <v>124848583</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>88359</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457050</v>
+        <v>456916</v>
       </c>
       <c r="R5" t="n">
-        <v>6925282</v>
+        <v>6925584</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848583</v>
+        <v>124848578</v>
       </c>
       <c r="B6" t="n">
-        <v>88359</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456916</v>
+        <v>456928</v>
       </c>
       <c r="R6" t="n">
-        <v>6925584</v>
+        <v>6925545</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848549</v>
+        <v>124848573</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>78889</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457151</v>
+        <v>457004</v>
       </c>
       <c r="R7" t="n">
-        <v>6925474</v>
+        <v>6925576</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848576</v>
+        <v>124848549</v>
       </c>
       <c r="B8" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457051</v>
+        <v>457151</v>
       </c>
       <c r="R8" t="n">
-        <v>6925537</v>
+        <v>6925474</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1381,7 +1376,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1400,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848546</v>
+        <v>124848545</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>78905</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>967</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1440,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457165</v>
+        <v>456823</v>
       </c>
       <c r="R9" t="n">
-        <v>6925267</v>
+        <v>6925376</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1609,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848548</v>
+        <v>124848551</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1649,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457064</v>
+        <v>457116</v>
       </c>
       <c r="R11" t="n">
-        <v>6925274</v>
+        <v>6925215</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,6 +1679,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1711,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848547</v>
+        <v>124848576</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1751,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456911</v>
+        <v>457051</v>
       </c>
       <c r="R12" t="n">
-        <v>6925161</v>
+        <v>6925537</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,6 +1794,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1920,10 +1920,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848551</v>
+        <v>124848584</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,21 +1936,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457116</v>
+        <v>456896</v>
       </c>
       <c r="R14" t="n">
-        <v>6925215</v>
+        <v>6925616</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1996,11 +1996,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2027,7 +2022,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848558</v>
+        <v>124848560</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2067,10 +2062,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457197</v>
+        <v>457173</v>
       </c>
       <c r="R15" t="n">
-        <v>6925420</v>
+        <v>6925356</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,7 +2102,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2134,7 +2129,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848555</v>
+        <v>124848557</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2174,10 +2169,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457075</v>
+        <v>457156</v>
       </c>
       <c r="R16" t="n">
-        <v>6925276</v>
+        <v>6925470</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,7 +2209,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack färska på tall</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2241,10 +2236,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124848557</v>
+        <v>124848547</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2257,21 +2252,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2281,10 +2276,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457156</v>
+        <v>456911</v>
       </c>
       <c r="R17" t="n">
-        <v>6925470</v>
+        <v>6925161</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2317,11 +2312,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2348,10 +2338,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124848545</v>
+        <v>124848555</v>
       </c>
       <c r="B18" t="n">
-        <v>78905</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2364,21 +2354,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>967</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2388,10 +2378,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456823</v>
+        <v>457075</v>
       </c>
       <c r="R18" t="n">
-        <v>6925376</v>
+        <v>6925276</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,6 +2414,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2557,10 +2552,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124848584</v>
+        <v>124848558</v>
       </c>
       <c r="B20" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2573,21 +2568,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2597,10 +2592,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456896</v>
+        <v>457197</v>
       </c>
       <c r="R20" t="n">
-        <v>6925616</v>
+        <v>6925420</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2633,6 +2628,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2659,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124848573</v>
+        <v>124848577</v>
       </c>
       <c r="B21" t="n">
-        <v>78889</v>
+        <v>91008</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,21 +2675,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457004</v>
+        <v>457050</v>
       </c>
       <c r="R21" t="n">
-        <v>6925576</v>
+        <v>6925282</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848548</v>
+        <v>124848576</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457064</v>
+        <v>457051</v>
       </c>
       <c r="R2" t="n">
-        <v>6925274</v>
+        <v>6925537</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +759,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848546</v>
+        <v>124848545</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>78905</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +794,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>967</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457165</v>
+        <v>456823</v>
       </c>
       <c r="R3" t="n">
-        <v>6925267</v>
+        <v>6925376</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +880,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848554</v>
+        <v>124848579</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456857</v>
+        <v>456957</v>
       </c>
       <c r="R4" t="n">
-        <v>6925333</v>
+        <v>6925524</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +960,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +987,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848583</v>
+        <v>124848551</v>
       </c>
       <c r="B5" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1003,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456916</v>
+        <v>457116</v>
       </c>
       <c r="R5" t="n">
-        <v>6925584</v>
+        <v>6925215</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1063,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848578</v>
+        <v>124848553</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456928</v>
+        <v>456909</v>
       </c>
       <c r="R6" t="n">
-        <v>6925545</v>
+        <v>6925153</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,6 +1170,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1201,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848573</v>
+        <v>124848549</v>
       </c>
       <c r="B7" t="n">
-        <v>78889</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1217,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457004</v>
+        <v>457151</v>
       </c>
       <c r="R7" t="n">
-        <v>6925576</v>
+        <v>6925474</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1303,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848549</v>
+        <v>124848578</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1319,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1343,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457151</v>
+        <v>456928</v>
       </c>
       <c r="R8" t="n">
-        <v>6925474</v>
+        <v>6925545</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1405,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848545</v>
+        <v>124848560</v>
       </c>
       <c r="B9" t="n">
-        <v>78905</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1421,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>967</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456823</v>
+        <v>457173</v>
       </c>
       <c r="R9" t="n">
-        <v>6925376</v>
+        <v>6925356</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1470,6 +1481,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,7 +1512,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848556</v>
+        <v>124848555</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1536,10 +1552,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456917</v>
+        <v>457075</v>
       </c>
       <c r="R10" t="n">
-        <v>6925573</v>
+        <v>6925276</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1592,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,7 +1619,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848551</v>
+        <v>124848557</v>
       </c>
       <c r="B11" t="n">
         <v>57513</v>
@@ -1643,10 +1659,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457116</v>
+        <v>457156</v>
       </c>
       <c r="R11" t="n">
-        <v>6925215</v>
+        <v>6925470</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,7 +1699,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska på tall</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,10 +1726,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848576</v>
+        <v>124848573</v>
       </c>
       <c r="B12" t="n">
-        <v>91008</v>
+        <v>78889</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1742,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1766,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457051</v>
+        <v>457004</v>
       </c>
       <c r="R12" t="n">
-        <v>6925537</v>
+        <v>6925576</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1794,7 +1810,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1813,10 +1828,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848579</v>
+        <v>124848554</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,21 +1844,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1868,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456957</v>
+        <v>456857</v>
       </c>
       <c r="R13" t="n">
-        <v>6925524</v>
+        <v>6925333</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,7 +1908,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1920,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848584</v>
+        <v>124848556</v>
       </c>
       <c r="B14" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,21 +1951,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1960,10 +1975,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456896</v>
+        <v>456917</v>
       </c>
       <c r="R14" t="n">
-        <v>6925616</v>
+        <v>6925573</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1996,6 +2011,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2022,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848560</v>
+        <v>124848546</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2038,21 +2058,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2062,10 +2082,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457173</v>
+        <v>457165</v>
       </c>
       <c r="R15" t="n">
-        <v>6925356</v>
+        <v>6925267</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2098,11 +2118,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2129,10 +2144,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848557</v>
+        <v>124848547</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2145,21 +2160,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2169,10 +2184,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457156</v>
+        <v>456911</v>
       </c>
       <c r="R16" t="n">
-        <v>6925470</v>
+        <v>6925161</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,11 +2220,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2236,10 +2246,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124848547</v>
+        <v>124848584</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2252,21 +2262,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2276,10 +2286,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456911</v>
+        <v>456896</v>
       </c>
       <c r="R17" t="n">
-        <v>6925161</v>
+        <v>6925616</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2338,10 +2348,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124848555</v>
+        <v>124848548</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2354,21 +2364,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2378,10 +2388,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457075</v>
+        <v>457064</v>
       </c>
       <c r="R18" t="n">
-        <v>6925276</v>
+        <v>6925274</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,11 +2424,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2445,10 +2450,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124848553</v>
+        <v>124848583</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2461,21 +2466,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2485,10 +2490,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456909</v>
+        <v>456916</v>
       </c>
       <c r="R19" t="n">
-        <v>6925153</v>
+        <v>6925584</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,11 +2526,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2552,10 +2552,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124848558</v>
+        <v>124848577</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457197</v>
+        <v>457050</v>
       </c>
       <c r="R20" t="n">
-        <v>6925420</v>
+        <v>6925282</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,11 +2628,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2659,10 +2654,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124848577</v>
+        <v>124848558</v>
       </c>
       <c r="B21" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,21 +2670,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2699,10 +2694,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457050</v>
+        <v>457197</v>
       </c>
       <c r="R21" t="n">
-        <v>6925282</v>
+        <v>6925420</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,6 +2730,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848576</v>
+        <v>124848553</v>
       </c>
       <c r="B2" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457051</v>
+        <v>456909</v>
       </c>
       <c r="R2" t="n">
-        <v>6925537</v>
+        <v>6925153</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,13 +753,17 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre på tall</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -880,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848579</v>
+        <v>124848548</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456957</v>
+        <v>457064</v>
       </c>
       <c r="R4" t="n">
-        <v>6925524</v>
+        <v>6925274</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848551</v>
+        <v>124848555</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1027,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457116</v>
+        <v>457075</v>
       </c>
       <c r="R5" t="n">
-        <v>6925215</v>
+        <v>6925276</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848553</v>
+        <v>124848573</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456909</v>
+        <v>457004</v>
       </c>
       <c r="R6" t="n">
-        <v>6925153</v>
+        <v>6925576</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848549</v>
+        <v>124848554</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1241,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457151</v>
+        <v>456857</v>
       </c>
       <c r="R7" t="n">
-        <v>6925474</v>
+        <v>6925333</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848578</v>
+        <v>124848560</v>
       </c>
       <c r="B8" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1343,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456928</v>
+        <v>457173</v>
       </c>
       <c r="R8" t="n">
-        <v>6925545</v>
+        <v>6925356</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1379,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848560</v>
+        <v>124848578</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1445,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457173</v>
+        <v>456928</v>
       </c>
       <c r="R9" t="n">
-        <v>6925356</v>
+        <v>6925545</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,11 +1485,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1512,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848555</v>
+        <v>124848557</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1552,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457075</v>
+        <v>457156</v>
       </c>
       <c r="R10" t="n">
-        <v>6925276</v>
+        <v>6925470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,7 +1591,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska på tall</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1619,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848557</v>
+        <v>124848549</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1635,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1659,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457156</v>
+        <v>457151</v>
       </c>
       <c r="R11" t="n">
-        <v>6925470</v>
+        <v>6925474</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,11 +1694,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1726,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848573</v>
+        <v>124848576</v>
       </c>
       <c r="B12" t="n">
-        <v>78889</v>
+        <v>91008</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1742,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1766,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457004</v>
+        <v>457051</v>
       </c>
       <c r="R12" t="n">
-        <v>6925576</v>
+        <v>6925537</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,6 +1804,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1828,7 +1823,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848554</v>
+        <v>124848551</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1868,10 +1863,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456857</v>
+        <v>457116</v>
       </c>
       <c r="R13" t="n">
-        <v>6925333</v>
+        <v>6925215</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,7 +1903,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,7 +2037,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848546</v>
+        <v>124848547</v>
       </c>
       <c r="B15" t="n">
         <v>91012</v>
@@ -2082,10 +2077,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457165</v>
+        <v>456911</v>
       </c>
       <c r="R15" t="n">
-        <v>6925267</v>
+        <v>6925161</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2144,10 +2139,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848547</v>
+        <v>124848584</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2160,21 +2155,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2184,10 +2179,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456911</v>
+        <v>456896</v>
       </c>
       <c r="R16" t="n">
-        <v>6925161</v>
+        <v>6925616</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2246,10 +2241,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124848584</v>
+        <v>124848577</v>
       </c>
       <c r="B17" t="n">
-        <v>88359</v>
+        <v>91008</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2262,21 +2257,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2286,10 +2281,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456896</v>
+        <v>457050</v>
       </c>
       <c r="R17" t="n">
-        <v>6925616</v>
+        <v>6925282</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2348,10 +2343,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124848548</v>
+        <v>124848583</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2364,21 +2359,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2388,10 +2383,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457064</v>
+        <v>456916</v>
       </c>
       <c r="R18" t="n">
-        <v>6925274</v>
+        <v>6925584</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,10 +2445,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124848583</v>
+        <v>124848546</v>
       </c>
       <c r="B19" t="n">
-        <v>88359</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2466,21 +2461,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2490,10 +2485,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456916</v>
+        <v>457165</v>
       </c>
       <c r="R19" t="n">
-        <v>6925584</v>
+        <v>6925267</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2552,10 +2547,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124848577</v>
+        <v>124848579</v>
       </c>
       <c r="B20" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2568,21 +2563,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2592,10 +2587,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457050</v>
+        <v>456957</v>
       </c>
       <c r="R20" t="n">
-        <v>6925282</v>
+        <v>6925524</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,6 +2623,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848553</v>
+        <v>124848554</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456909</v>
+        <v>456857</v>
       </c>
       <c r="R2" t="n">
-        <v>6925153</v>
+        <v>6925333</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ringhack äldre på tall</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848545</v>
+        <v>124848558</v>
       </c>
       <c r="B3" t="n">
-        <v>78905</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>967</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456823</v>
+        <v>457197</v>
       </c>
       <c r="R3" t="n">
-        <v>6925376</v>
+        <v>6925420</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848555</v>
+        <v>124848549</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457075</v>
+        <v>457151</v>
       </c>
       <c r="R5" t="n">
-        <v>6925276</v>
+        <v>6925474</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848573</v>
+        <v>124848578</v>
       </c>
       <c r="B6" t="n">
-        <v>78889</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457004</v>
+        <v>456928</v>
       </c>
       <c r="R6" t="n">
-        <v>6925576</v>
+        <v>6925545</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848554</v>
+        <v>124848576</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456857</v>
+        <v>457051</v>
       </c>
       <c r="R7" t="n">
-        <v>6925333</v>
+        <v>6925537</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,17 +1273,13 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1302,10 +1298,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848560</v>
+        <v>124848546</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1314,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457173</v>
+        <v>457165</v>
       </c>
       <c r="R8" t="n">
-        <v>6925356</v>
+        <v>6925267</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,11 +1374,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1400,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848578</v>
+        <v>124848551</v>
       </c>
       <c r="B9" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1416,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456928</v>
+        <v>457116</v>
       </c>
       <c r="R9" t="n">
-        <v>6925545</v>
+        <v>6925215</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,6 +1476,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848557</v>
+        <v>124848577</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1523,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457156</v>
+        <v>457050</v>
       </c>
       <c r="R10" t="n">
-        <v>6925470</v>
+        <v>6925282</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,11 +1583,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848549</v>
+        <v>124848584</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1625,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457151</v>
+        <v>456896</v>
       </c>
       <c r="R11" t="n">
-        <v>6925474</v>
+        <v>6925616</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1711,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848576</v>
+        <v>124848545</v>
       </c>
       <c r="B12" t="n">
-        <v>91008</v>
+        <v>78905</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1727,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>967</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1751,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457051</v>
+        <v>456823</v>
       </c>
       <c r="R12" t="n">
-        <v>6925537</v>
+        <v>6925376</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,7 +1795,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1823,10 +1813,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848551</v>
+        <v>124848573</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1839,21 +1829,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1863,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457116</v>
+        <v>457004</v>
       </c>
       <c r="R13" t="n">
-        <v>6925215</v>
+        <v>6925576</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,11 +1889,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2037,10 +2022,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848547</v>
+        <v>124848560</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2053,21 +2038,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2077,10 +2062,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456911</v>
+        <v>457173</v>
       </c>
       <c r="R15" t="n">
-        <v>6925161</v>
+        <v>6925356</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2113,6 +2098,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2139,7 +2129,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848584</v>
+        <v>124848583</v>
       </c>
       <c r="B16" t="n">
         <v>88359</v>
@@ -2179,10 +2169,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456896</v>
+        <v>456916</v>
       </c>
       <c r="R16" t="n">
-        <v>6925616</v>
+        <v>6925584</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2241,10 +2231,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124848577</v>
+        <v>124848547</v>
       </c>
       <c r="B17" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2257,21 +2247,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2281,10 +2271,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457050</v>
+        <v>456911</v>
       </c>
       <c r="R17" t="n">
-        <v>6925282</v>
+        <v>6925161</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2343,10 +2333,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124848583</v>
+        <v>124848553</v>
       </c>
       <c r="B18" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2359,21 +2349,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2383,10 +2373,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456916</v>
+        <v>456909</v>
       </c>
       <c r="R18" t="n">
-        <v>6925584</v>
+        <v>6925153</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,6 +2409,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2445,10 +2440,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124848546</v>
+        <v>124848557</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2461,21 +2456,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2485,10 +2480,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457165</v>
+        <v>457156</v>
       </c>
       <c r="R19" t="n">
-        <v>6925267</v>
+        <v>6925470</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,6 +2516,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2654,7 +2654,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124848558</v>
+        <v>124848555</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2694,10 +2694,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457197</v>
+        <v>457075</v>
       </c>
       <c r="R21" t="n">
-        <v>6925420</v>
+        <v>6925276</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848554</v>
+        <v>124848578</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456857</v>
+        <v>456928</v>
       </c>
       <c r="R2" t="n">
-        <v>6925333</v>
+        <v>6925545</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848558</v>
+        <v>124848557</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457197</v>
+        <v>457156</v>
       </c>
       <c r="R3" t="n">
-        <v>6925420</v>
+        <v>6925470</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848548</v>
+        <v>124848556</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457064</v>
+        <v>456917</v>
       </c>
       <c r="R4" t="n">
-        <v>6925274</v>
+        <v>6925573</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848549</v>
+        <v>124848577</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457151</v>
+        <v>457050</v>
       </c>
       <c r="R5" t="n">
-        <v>6925474</v>
+        <v>6925282</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848578</v>
+        <v>124848555</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456928</v>
+        <v>457075</v>
       </c>
       <c r="R6" t="n">
-        <v>6925545</v>
+        <v>6925276</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848576</v>
+        <v>124848553</v>
       </c>
       <c r="B7" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457051</v>
+        <v>456909</v>
       </c>
       <c r="R7" t="n">
-        <v>6925537</v>
+        <v>6925153</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,13 +1278,17 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre på tall</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1298,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848546</v>
+        <v>124848551</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1338,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457165</v>
+        <v>457116</v>
       </c>
       <c r="R8" t="n">
-        <v>6925267</v>
+        <v>6925215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848551</v>
+        <v>124848548</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1440,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457116</v>
+        <v>457064</v>
       </c>
       <c r="R9" t="n">
-        <v>6925215</v>
+        <v>6925274</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1507,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848577</v>
+        <v>124848549</v>
       </c>
       <c r="B10" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457050</v>
+        <v>457151</v>
       </c>
       <c r="R10" t="n">
-        <v>6925282</v>
+        <v>6925474</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848584</v>
+        <v>124848554</v>
       </c>
       <c r="B11" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1649,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456896</v>
+        <v>456857</v>
       </c>
       <c r="R11" t="n">
-        <v>6925616</v>
+        <v>6925333</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,6 +1694,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1711,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848545</v>
+        <v>124848579</v>
       </c>
       <c r="B12" t="n">
-        <v>78905</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1751,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456823</v>
+        <v>456957</v>
       </c>
       <c r="R12" t="n">
-        <v>6925376</v>
+        <v>6925524</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,6 +1801,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1813,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848573</v>
+        <v>124848547</v>
       </c>
       <c r="B13" t="n">
-        <v>78889</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457004</v>
+        <v>456911</v>
       </c>
       <c r="R13" t="n">
-        <v>6925576</v>
+        <v>6925161</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848556</v>
+        <v>124848573</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1931,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1955,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456917</v>
+        <v>457004</v>
       </c>
       <c r="R14" t="n">
-        <v>6925573</v>
+        <v>6925576</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1991,11 +2010,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2022,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848560</v>
+        <v>124848546</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2038,21 +2052,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2062,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457173</v>
+        <v>457165</v>
       </c>
       <c r="R15" t="n">
-        <v>6925356</v>
+        <v>6925267</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2098,11 +2112,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2129,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848583</v>
+        <v>124848558</v>
       </c>
       <c r="B16" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2145,21 +2154,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2169,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456916</v>
+        <v>457197</v>
       </c>
       <c r="R16" t="n">
-        <v>6925584</v>
+        <v>6925420</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,6 +2214,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2231,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124848547</v>
+        <v>124848576</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2247,21 +2261,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2271,10 +2285,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456911</v>
+        <v>457051</v>
       </c>
       <c r="R17" t="n">
-        <v>6925161</v>
+        <v>6925537</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2315,6 +2329,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2333,10 +2348,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124848553</v>
+        <v>124848584</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2349,21 +2364,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2373,10 +2388,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456909</v>
+        <v>456896</v>
       </c>
       <c r="R18" t="n">
-        <v>6925153</v>
+        <v>6925616</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,11 +2424,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2440,10 +2450,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124848557</v>
+        <v>124848545</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>78905</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2456,21 +2466,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>967</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2480,10 +2490,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457156</v>
+        <v>456823</v>
       </c>
       <c r="R19" t="n">
-        <v>6925470</v>
+        <v>6925376</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,11 +2526,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2547,10 +2552,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124848579</v>
+        <v>124848560</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2563,21 +2568,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2587,10 +2592,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456957</v>
+        <v>457173</v>
       </c>
       <c r="R20" t="n">
-        <v>6925524</v>
+        <v>6925356</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2627,7 +2632,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2654,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124848555</v>
+        <v>124848583</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2670,21 +2675,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2694,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457075</v>
+        <v>456916</v>
       </c>
       <c r="R21" t="n">
-        <v>6925276</v>
+        <v>6925584</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,11 +2735,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848546</v>
+        <v>124848558</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2052,21 +2052,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457165</v>
+        <v>457197</v>
       </c>
       <c r="R15" t="n">
-        <v>6925267</v>
+        <v>6925420</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,6 +2112,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2138,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848558</v>
+        <v>124848546</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2154,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457197</v>
+        <v>457165</v>
       </c>
       <c r="R16" t="n">
-        <v>6925420</v>
+        <v>6925267</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,11 +2219,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848557</v>
+        <v>124848556</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457156</v>
+        <v>456917</v>
       </c>
       <c r="R3" t="n">
-        <v>6925470</v>
+        <v>6925573</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848556</v>
+        <v>124848557</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456917</v>
+        <v>457156</v>
       </c>
       <c r="R4" t="n">
-        <v>6925573</v>
+        <v>6925470</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -2036,10 +2036,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848558</v>
+        <v>124848546</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2052,21 +2052,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457197</v>
+        <v>457165</v>
       </c>
       <c r="R15" t="n">
-        <v>6925420</v>
+        <v>6925267</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,11 +2112,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,10 +2138,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848546</v>
+        <v>124848558</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,21 +2154,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2178,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457165</v>
+        <v>457197</v>
       </c>
       <c r="R16" t="n">
-        <v>6925267</v>
+        <v>6925420</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,6 +2214,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848578</v>
+        <v>124848576</v>
       </c>
       <c r="B2" t="n">
         <v>91008</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456928</v>
+        <v>457051</v>
       </c>
       <c r="R2" t="n">
-        <v>6925545</v>
+        <v>6925537</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,6 +759,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848556</v>
+        <v>124848573</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +794,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456917</v>
+        <v>457004</v>
       </c>
       <c r="R3" t="n">
-        <v>6925573</v>
+        <v>6925576</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +854,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -991,10 +987,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848577</v>
+        <v>124848546</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1003,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457050</v>
+        <v>457165</v>
       </c>
       <c r="R5" t="n">
-        <v>6925282</v>
+        <v>6925267</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1089,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848555</v>
+        <v>124848558</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1133,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457075</v>
+        <v>457197</v>
       </c>
       <c r="R6" t="n">
-        <v>6925276</v>
+        <v>6925420</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1169,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack färska på tall</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848553</v>
+        <v>124848547</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1212,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456909</v>
+        <v>456911</v>
       </c>
       <c r="R7" t="n">
-        <v>6925153</v>
+        <v>6925161</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1272,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1298,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848551</v>
+        <v>124848545</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>78905</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1314,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>967</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457116</v>
+        <v>456823</v>
       </c>
       <c r="R8" t="n">
-        <v>6925215</v>
+        <v>6925376</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,11 +1374,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1400,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848548</v>
+        <v>124848551</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1416,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457064</v>
+        <v>457116</v>
       </c>
       <c r="R9" t="n">
-        <v>6925274</v>
+        <v>6925215</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1476,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848549</v>
+        <v>124848553</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1523,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457151</v>
+        <v>456909</v>
       </c>
       <c r="R10" t="n">
-        <v>6925474</v>
+        <v>6925153</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,6 +1583,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1614,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848554</v>
+        <v>124848579</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1630,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456857</v>
+        <v>456957</v>
       </c>
       <c r="R11" t="n">
-        <v>6925333</v>
+        <v>6925524</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1694,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1721,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848579</v>
+        <v>124848577</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,21 +1737,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1761,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456957</v>
+        <v>457050</v>
       </c>
       <c r="R12" t="n">
-        <v>6925524</v>
+        <v>6925282</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,11 +1797,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1823,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848547</v>
+        <v>124848556</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1839,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1863,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456911</v>
+        <v>456917</v>
       </c>
       <c r="R13" t="n">
-        <v>6925161</v>
+        <v>6925573</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,6 +1899,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1930,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848573</v>
+        <v>124848578</v>
       </c>
       <c r="B14" t="n">
-        <v>78889</v>
+        <v>91008</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1946,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1970,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457004</v>
+        <v>456928</v>
       </c>
       <c r="R14" t="n">
-        <v>6925576</v>
+        <v>6925545</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2036,10 +2032,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848546</v>
+        <v>124848583</v>
       </c>
       <c r="B15" t="n">
-        <v>91012</v>
+        <v>88359</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2052,21 +2048,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2072,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457165</v>
+        <v>456916</v>
       </c>
       <c r="R15" t="n">
-        <v>6925267</v>
+        <v>6925584</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2138,10 +2134,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848558</v>
+        <v>124848549</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2154,21 +2150,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2174,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457197</v>
+        <v>457151</v>
       </c>
       <c r="R16" t="n">
-        <v>6925420</v>
+        <v>6925474</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,11 +2210,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2245,10 +2236,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124848576</v>
+        <v>124848560</v>
       </c>
       <c r="B17" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2261,21 +2252,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2285,10 +2276,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457051</v>
+        <v>457173</v>
       </c>
       <c r="R17" t="n">
-        <v>6925537</v>
+        <v>6925356</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2323,13 +2314,17 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2348,10 +2343,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124848584</v>
+        <v>124848555</v>
       </c>
       <c r="B18" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2364,21 +2359,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2388,10 +2383,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456896</v>
+        <v>457075</v>
       </c>
       <c r="R18" t="n">
-        <v>6925616</v>
+        <v>6925276</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2424,6 +2419,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2450,10 +2450,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124848545</v>
+        <v>124848584</v>
       </c>
       <c r="B19" t="n">
-        <v>78905</v>
+        <v>88359</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2466,21 +2466,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>967</v>
+        <v>510</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2490,10 +2490,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456823</v>
+        <v>456896</v>
       </c>
       <c r="R19" t="n">
-        <v>6925376</v>
+        <v>6925616</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124848560</v>
+        <v>124848548</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457173</v>
+        <v>457064</v>
       </c>
       <c r="R20" t="n">
-        <v>6925356</v>
+        <v>6925274</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,11 +2628,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2659,10 +2654,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124848583</v>
+        <v>124848554</v>
       </c>
       <c r="B21" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,21 +2670,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2699,10 +2694,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456916</v>
+        <v>456857</v>
       </c>
       <c r="R21" t="n">
-        <v>6925584</v>
+        <v>6925333</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,6 +2730,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848576</v>
+        <v>124848547</v>
       </c>
       <c r="B2" t="n">
-        <v>91008</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457051</v>
+        <v>456911</v>
       </c>
       <c r="R2" t="n">
-        <v>6925537</v>
+        <v>6925161</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -778,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848573</v>
+        <v>124848549</v>
       </c>
       <c r="B3" t="n">
-        <v>78889</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457004</v>
+        <v>457151</v>
       </c>
       <c r="R3" t="n">
-        <v>6925576</v>
+        <v>6925474</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848557</v>
+        <v>124848548</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457156</v>
+        <v>457064</v>
       </c>
       <c r="R4" t="n">
-        <v>6925470</v>
+        <v>6925274</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848546</v>
+        <v>124848576</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1027,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457165</v>
+        <v>457051</v>
       </c>
       <c r="R5" t="n">
-        <v>6925267</v>
+        <v>6925537</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,6 +1065,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1089,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848558</v>
+        <v>124848579</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1129,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457197</v>
+        <v>456957</v>
       </c>
       <c r="R6" t="n">
-        <v>6925420</v>
+        <v>6925524</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,7 +1164,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,10 +1191,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848547</v>
+        <v>124848553</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,21 +1207,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1236,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456911</v>
+        <v>456909</v>
       </c>
       <c r="R7" t="n">
-        <v>6925161</v>
+        <v>6925153</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,6 +1267,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1298,10 +1298,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848545</v>
+        <v>124848560</v>
       </c>
       <c r="B8" t="n">
-        <v>78905</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,21 +1314,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>967</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>456823</v>
+        <v>457173</v>
       </c>
       <c r="R8" t="n">
-        <v>6925376</v>
+        <v>6925356</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,6 +1374,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,7 +1405,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848551</v>
+        <v>124848556</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1440,10 +1445,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457116</v>
+        <v>456917</v>
       </c>
       <c r="R9" t="n">
-        <v>6925215</v>
+        <v>6925573</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,7 +1485,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska på tall</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1507,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848553</v>
+        <v>124848583</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,21 +1528,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1552,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456909</v>
+        <v>456916</v>
       </c>
       <c r="R10" t="n">
-        <v>6925153</v>
+        <v>6925584</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1583,11 +1588,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1614,10 +1614,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848579</v>
+        <v>124848551</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,21 +1630,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456957</v>
+        <v>457116</v>
       </c>
       <c r="R11" t="n">
-        <v>6925524</v>
+        <v>6925215</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1721,10 +1721,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848577</v>
+        <v>124848558</v>
       </c>
       <c r="B12" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1737,21 +1737,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1761,10 +1761,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457050</v>
+        <v>457197</v>
       </c>
       <c r="R12" t="n">
-        <v>6925282</v>
+        <v>6925420</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,6 +1797,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1823,7 +1828,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848556</v>
+        <v>124848557</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -1863,10 +1868,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456917</v>
+        <v>457156</v>
       </c>
       <c r="R13" t="n">
-        <v>6925573</v>
+        <v>6925470</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848578</v>
+        <v>124848555</v>
       </c>
       <c r="B14" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1946,21 +1951,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1970,10 +1975,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456928</v>
+        <v>457075</v>
       </c>
       <c r="R14" t="n">
-        <v>6925545</v>
+        <v>6925276</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,6 +2011,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2032,10 +2042,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848583</v>
+        <v>124848573</v>
       </c>
       <c r="B15" t="n">
-        <v>88359</v>
+        <v>78889</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2048,21 +2058,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2072,10 +2082,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456916</v>
+        <v>457004</v>
       </c>
       <c r="R15" t="n">
-        <v>6925584</v>
+        <v>6925576</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2134,10 +2144,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848549</v>
+        <v>124848578</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2150,21 +2160,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2174,10 +2184,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457151</v>
+        <v>456928</v>
       </c>
       <c r="R16" t="n">
-        <v>6925474</v>
+        <v>6925545</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2236,7 +2246,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124848560</v>
+        <v>124848554</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2276,10 +2286,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457173</v>
+        <v>456857</v>
       </c>
       <c r="R17" t="n">
-        <v>6925356</v>
+        <v>6925333</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,7 +2326,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska på tall</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2343,10 +2353,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124848555</v>
+        <v>124848545</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>78905</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2359,21 +2369,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>967</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2383,10 +2393,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457075</v>
+        <v>456823</v>
       </c>
       <c r="R18" t="n">
-        <v>6925276</v>
+        <v>6925376</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2419,11 +2429,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2450,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124848584</v>
+        <v>124848577</v>
       </c>
       <c r="B19" t="n">
-        <v>88359</v>
+        <v>91008</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2466,21 +2471,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2490,10 +2495,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456896</v>
+        <v>457050</v>
       </c>
       <c r="R19" t="n">
-        <v>6925616</v>
+        <v>6925282</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2552,7 +2557,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124848548</v>
+        <v>124848546</v>
       </c>
       <c r="B20" t="n">
         <v>91012</v>
@@ -2592,10 +2597,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457064</v>
+        <v>457165</v>
       </c>
       <c r="R20" t="n">
-        <v>6925274</v>
+        <v>6925267</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2654,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124848554</v>
+        <v>124848584</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2670,21 +2675,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2694,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456857</v>
+        <v>456896</v>
       </c>
       <c r="R21" t="n">
-        <v>6925333</v>
+        <v>6925616</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,11 +2735,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848547</v>
+        <v>124848577</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456911</v>
+        <v>457050</v>
       </c>
       <c r="R2" t="n">
-        <v>6925161</v>
+        <v>6925282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848549</v>
+        <v>124848557</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457151</v>
+        <v>457156</v>
       </c>
       <c r="R3" t="n">
-        <v>6925474</v>
+        <v>6925470</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848548</v>
+        <v>124848554</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457064</v>
+        <v>456857</v>
       </c>
       <c r="R4" t="n">
-        <v>6925274</v>
+        <v>6925333</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1084,10 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848579</v>
+        <v>124848548</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1124,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456957</v>
+        <v>457064</v>
       </c>
       <c r="R6" t="n">
-        <v>6925524</v>
+        <v>6925274</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,11 +1170,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1191,10 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848553</v>
+        <v>124848584</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,21 +1212,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1231,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456909</v>
+        <v>456896</v>
       </c>
       <c r="R7" t="n">
-        <v>6925153</v>
+        <v>6925616</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,11 +1272,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1298,10 +1298,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848560</v>
+        <v>124848573</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,21 +1314,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457173</v>
+        <v>457004</v>
       </c>
       <c r="R8" t="n">
-        <v>6925356</v>
+        <v>6925576</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,11 +1374,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,10 +1400,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848556</v>
+        <v>124848545</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>78905</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,21 +1416,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>967</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1445,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456917</v>
+        <v>456823</v>
       </c>
       <c r="R9" t="n">
-        <v>6925573</v>
+        <v>6925376</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,11 +1476,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1512,10 +1502,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848583</v>
+        <v>124848555</v>
       </c>
       <c r="B10" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1528,21 +1518,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1552,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456916</v>
+        <v>457075</v>
       </c>
       <c r="R10" t="n">
-        <v>6925584</v>
+        <v>6925276</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1588,6 +1578,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1614,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848551</v>
+        <v>124848546</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,21 +1625,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1654,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457116</v>
+        <v>457165</v>
       </c>
       <c r="R11" t="n">
-        <v>6925215</v>
+        <v>6925267</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1690,11 +1685,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1721,7 +1711,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848558</v>
+        <v>124848553</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1761,10 +1751,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457197</v>
+        <v>456909</v>
       </c>
       <c r="R12" t="n">
-        <v>6925420</v>
+        <v>6925153</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,7 +1791,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1828,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848557</v>
+        <v>124848547</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1844,21 +1834,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1868,10 +1858,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457156</v>
+        <v>456911</v>
       </c>
       <c r="R13" t="n">
-        <v>6925470</v>
+        <v>6925161</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,11 +1894,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1935,10 +1920,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848555</v>
+        <v>124848579</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1951,21 +1936,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1975,10 +1960,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457075</v>
+        <v>456957</v>
       </c>
       <c r="R14" t="n">
-        <v>6925276</v>
+        <v>6925524</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,7 +2000,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack färska på tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2042,10 +2027,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848573</v>
+        <v>124848583</v>
       </c>
       <c r="B15" t="n">
-        <v>78889</v>
+        <v>88359</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2058,21 +2043,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>864</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2082,10 +2067,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457004</v>
+        <v>456916</v>
       </c>
       <c r="R15" t="n">
-        <v>6925576</v>
+        <v>6925584</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2144,10 +2129,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848578</v>
+        <v>124848556</v>
       </c>
       <c r="B16" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2160,21 +2145,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2184,10 +2169,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456928</v>
+        <v>456917</v>
       </c>
       <c r="R16" t="n">
-        <v>6925545</v>
+        <v>6925573</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2220,6 +2205,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2246,7 +2236,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124848554</v>
+        <v>124848560</v>
       </c>
       <c r="B17" t="n">
         <v>57513</v>
@@ -2286,10 +2276,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456857</v>
+        <v>457173</v>
       </c>
       <c r="R17" t="n">
-        <v>6925333</v>
+        <v>6925356</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,7 +2316,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2353,10 +2343,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124848545</v>
+        <v>124848578</v>
       </c>
       <c r="B18" t="n">
-        <v>78905</v>
+        <v>91008</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2369,21 +2359,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>967</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2393,10 +2383,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456823</v>
+        <v>456928</v>
       </c>
       <c r="R18" t="n">
-        <v>6925376</v>
+        <v>6925545</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,10 +2445,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124848577</v>
+        <v>124848558</v>
       </c>
       <c r="B19" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2471,21 +2461,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2495,10 +2485,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457050</v>
+        <v>457197</v>
       </c>
       <c r="R19" t="n">
-        <v>6925282</v>
+        <v>6925420</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,6 +2521,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2557,7 +2552,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124848546</v>
+        <v>124848549</v>
       </c>
       <c r="B20" t="n">
         <v>91012</v>
@@ -2597,10 +2592,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457165</v>
+        <v>457151</v>
       </c>
       <c r="R20" t="n">
-        <v>6925267</v>
+        <v>6925474</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,10 +2654,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124848584</v>
+        <v>124848551</v>
       </c>
       <c r="B21" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,21 +2670,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2699,10 +2694,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456896</v>
+        <v>457116</v>
       </c>
       <c r="R21" t="n">
-        <v>6925616</v>
+        <v>6925215</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,6 +2730,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -1818,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848547</v>
+        <v>124848579</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,21 +1834,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1858,10 +1858,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456911</v>
+        <v>456957</v>
       </c>
       <c r="R13" t="n">
-        <v>6925161</v>
+        <v>6925524</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1894,6 +1894,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1920,10 +1925,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848579</v>
+        <v>124848547</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,21 +1941,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1960,10 +1965,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456957</v>
+        <v>456911</v>
       </c>
       <c r="R14" t="n">
-        <v>6925524</v>
+        <v>6925161</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1996,11 +2001,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848577</v>
+        <v>124848583</v>
       </c>
       <c r="B2" t="n">
-        <v>91008</v>
+        <v>88359</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457050</v>
+        <v>456916</v>
       </c>
       <c r="R2" t="n">
-        <v>6925282</v>
+        <v>6925584</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848557</v>
+        <v>124848584</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>88359</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457156</v>
+        <v>456896</v>
       </c>
       <c r="R3" t="n">
-        <v>6925470</v>
+        <v>6925616</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848554</v>
+        <v>124848579</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456857</v>
+        <v>456957</v>
       </c>
       <c r="R4" t="n">
-        <v>6925333</v>
+        <v>6925524</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848576</v>
+        <v>124848577</v>
       </c>
       <c r="B5" t="n">
         <v>91008</v>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457051</v>
+        <v>457050</v>
       </c>
       <c r="R5" t="n">
-        <v>6925537</v>
+        <v>6925282</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1070,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1094,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848548</v>
+        <v>124848554</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457064</v>
+        <v>456857</v>
       </c>
       <c r="R6" t="n">
-        <v>6925274</v>
+        <v>6925333</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1196,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848584</v>
+        <v>124848553</v>
       </c>
       <c r="B7" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1212,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1236,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456896</v>
+        <v>456909</v>
       </c>
       <c r="R7" t="n">
-        <v>6925616</v>
+        <v>6925153</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1272,6 +1271,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1298,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848573</v>
+        <v>124848548</v>
       </c>
       <c r="B8" t="n">
-        <v>78889</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1338,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457004</v>
+        <v>457064</v>
       </c>
       <c r="R8" t="n">
-        <v>6925576</v>
+        <v>6925274</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1400,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848545</v>
+        <v>124848551</v>
       </c>
       <c r="B9" t="n">
-        <v>78905</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>967</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1440,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456823</v>
+        <v>457116</v>
       </c>
       <c r="R9" t="n">
-        <v>6925376</v>
+        <v>6925215</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,6 +1480,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1502,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848555</v>
+        <v>124848573</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>78889</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,21 +1527,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1542,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457075</v>
+        <v>457004</v>
       </c>
       <c r="R10" t="n">
-        <v>6925276</v>
+        <v>6925576</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1578,11 +1587,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1609,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848546</v>
+        <v>124848578</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1649,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457165</v>
+        <v>456928</v>
       </c>
       <c r="R11" t="n">
-        <v>6925267</v>
+        <v>6925545</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,7 +1715,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848553</v>
+        <v>124848557</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1751,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456909</v>
+        <v>457156</v>
       </c>
       <c r="R12" t="n">
-        <v>6925153</v>
+        <v>6925470</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,7 +1795,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre på tall</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1818,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848579</v>
+        <v>124848546</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1858,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456957</v>
+        <v>457165</v>
       </c>
       <c r="R13" t="n">
-        <v>6925524</v>
+        <v>6925267</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1894,11 +1898,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1925,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848547</v>
+        <v>124848576</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1941,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1965,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456911</v>
+        <v>457051</v>
       </c>
       <c r="R14" t="n">
-        <v>6925161</v>
+        <v>6925537</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2009,6 +2008,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2027,10 +2027,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848583</v>
+        <v>124848560</v>
       </c>
       <c r="B15" t="n">
-        <v>88359</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2043,21 +2043,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>456916</v>
+        <v>457173</v>
       </c>
       <c r="R15" t="n">
-        <v>6925584</v>
+        <v>6925356</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,6 +2103,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2129,10 +2134,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848556</v>
+        <v>124848547</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2145,21 +2150,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2169,10 +2174,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456917</v>
+        <v>456911</v>
       </c>
       <c r="R16" t="n">
-        <v>6925573</v>
+        <v>6925161</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,11 +2210,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2236,10 +2236,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124848560</v>
+        <v>124848549</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2252,21 +2252,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457173</v>
+        <v>457151</v>
       </c>
       <c r="R17" t="n">
-        <v>6925356</v>
+        <v>6925474</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,11 +2312,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2343,10 +2338,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124848578</v>
+        <v>124848545</v>
       </c>
       <c r="B18" t="n">
-        <v>91008</v>
+        <v>78905</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2359,21 +2354,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>967</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2383,10 +2378,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456928</v>
+        <v>456823</v>
       </c>
       <c r="R18" t="n">
-        <v>6925545</v>
+        <v>6925376</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2552,10 +2547,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124848549</v>
+        <v>124848555</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2568,21 +2563,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2592,10 +2587,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457151</v>
+        <v>457075</v>
       </c>
       <c r="R20" t="n">
-        <v>6925474</v>
+        <v>6925276</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,6 +2623,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2654,7 +2654,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124848551</v>
+        <v>124848556</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2694,10 +2694,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457116</v>
+        <v>456917</v>
       </c>
       <c r="R21" t="n">
-        <v>6925215</v>
+        <v>6925573</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack färska på tall</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -2338,10 +2338,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124848545</v>
+        <v>124848558</v>
       </c>
       <c r="B18" t="n">
-        <v>78905</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>967</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456823</v>
+        <v>457197</v>
       </c>
       <c r="R18" t="n">
-        <v>6925376</v>
+        <v>6925420</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,6 +2414,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2440,10 +2445,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124848558</v>
+        <v>124848545</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>78905</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2456,21 +2461,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>967</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2480,10 +2485,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>457197</v>
+        <v>456823</v>
       </c>
       <c r="R19" t="n">
-        <v>6925420</v>
+        <v>6925376</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2516,11 +2521,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848583</v>
+        <v>124848577</v>
       </c>
       <c r="B2" t="n">
-        <v>88359</v>
+        <v>91008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456916</v>
+        <v>457050</v>
       </c>
       <c r="R2" t="n">
-        <v>6925584</v>
+        <v>6925282</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848584</v>
+        <v>124848548</v>
       </c>
       <c r="B3" t="n">
-        <v>88359</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456896</v>
+        <v>457064</v>
       </c>
       <c r="R3" t="n">
-        <v>6925616</v>
+        <v>6925274</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848579</v>
+        <v>124848583</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>88359</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456957</v>
+        <v>456916</v>
       </c>
       <c r="R4" t="n">
-        <v>6925524</v>
+        <v>6925584</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848577</v>
+        <v>124848584</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>88359</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457050</v>
+        <v>456896</v>
       </c>
       <c r="R5" t="n">
-        <v>6925282</v>
+        <v>6925616</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848554</v>
+        <v>124848555</v>
       </c>
       <c r="B6" t="n">
         <v>57513</v>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>456857</v>
+        <v>457075</v>
       </c>
       <c r="R6" t="n">
-        <v>6925333</v>
+        <v>6925276</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1163,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848553</v>
+        <v>124848546</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>456909</v>
+        <v>457165</v>
       </c>
       <c r="R7" t="n">
-        <v>6925153</v>
+        <v>6925267</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848548</v>
+        <v>124848560</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457064</v>
+        <v>457173</v>
       </c>
       <c r="R8" t="n">
-        <v>6925274</v>
+        <v>6925356</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,6 +1368,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848573</v>
+        <v>124848545</v>
       </c>
       <c r="B10" t="n">
-        <v>78889</v>
+        <v>78905</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>967</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457004</v>
+        <v>456823</v>
       </c>
       <c r="R10" t="n">
-        <v>6925576</v>
+        <v>6925376</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848578</v>
+        <v>124848573</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
+        <v>78889</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456928</v>
+        <v>457004</v>
       </c>
       <c r="R11" t="n">
-        <v>6925545</v>
+        <v>6925576</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848557</v>
+        <v>124848553</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1755,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457156</v>
+        <v>456909</v>
       </c>
       <c r="R12" t="n">
-        <v>6925470</v>
+        <v>6925153</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,7 +1790,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,7 +1817,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848546</v>
+        <v>124848547</v>
       </c>
       <c r="B13" t="n">
         <v>91012</v>
@@ -1862,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457165</v>
+        <v>456911</v>
       </c>
       <c r="R13" t="n">
-        <v>6925267</v>
+        <v>6925161</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,7 +1919,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848576</v>
+        <v>124848578</v>
       </c>
       <c r="B14" t="n">
         <v>91008</v>
@@ -1964,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457051</v>
+        <v>456928</v>
       </c>
       <c r="R14" t="n">
-        <v>6925537</v>
+        <v>6925545</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2008,7 +2003,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2027,7 +2021,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848560</v>
+        <v>124848558</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2067,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457173</v>
+        <v>457197</v>
       </c>
       <c r="R15" t="n">
-        <v>6925356</v>
+        <v>6925420</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,7 +2101,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska på tall</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2134,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848547</v>
+        <v>124848576</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2150,21 +2144,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2174,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>456911</v>
+        <v>457051</v>
       </c>
       <c r="R16" t="n">
-        <v>6925161</v>
+        <v>6925537</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2218,6 +2212,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2236,10 +2231,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124848549</v>
+        <v>124848557</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2252,21 +2247,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2276,10 +2271,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457151</v>
+        <v>457156</v>
       </c>
       <c r="R17" t="n">
-        <v>6925474</v>
+        <v>6925470</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2312,6 +2307,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2338,7 +2338,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124848558</v>
+        <v>124848556</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457197</v>
+        <v>456917</v>
       </c>
       <c r="R18" t="n">
-        <v>6925420</v>
+        <v>6925573</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2445,10 +2445,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124848545</v>
+        <v>124848579</v>
       </c>
       <c r="B19" t="n">
-        <v>78905</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2461,21 +2461,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456823</v>
+        <v>456957</v>
       </c>
       <c r="R19" t="n">
-        <v>6925376</v>
+        <v>6925524</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2521,6 +2521,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2547,7 +2552,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124848555</v>
+        <v>124848554</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2587,10 +2592,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457075</v>
+        <v>456857</v>
       </c>
       <c r="R20" t="n">
-        <v>6925276</v>
+        <v>6925333</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2627,7 +2632,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack färska på tall</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2654,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124848556</v>
+        <v>124848549</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2670,21 +2675,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2694,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>456917</v>
+        <v>457151</v>
       </c>
       <c r="R21" t="n">
-        <v>6925573</v>
+        <v>6925474</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2730,11 +2735,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848577</v>
+        <v>124848579</v>
       </c>
       <c r="B2" t="n">
-        <v>91008</v>
+        <v>78947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457050</v>
+        <v>456957</v>
       </c>
       <c r="R2" t="n">
-        <v>6925282</v>
+        <v>6925524</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848548</v>
+        <v>124848584</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>88512</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457064</v>
+        <v>456896</v>
       </c>
       <c r="R3" t="n">
-        <v>6925274</v>
+        <v>6925616</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124848583</v>
+        <v>124848546</v>
       </c>
       <c r="B4" t="n">
-        <v>88359</v>
+        <v>91166</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>456916</v>
+        <v>457165</v>
       </c>
       <c r="R4" t="n">
-        <v>6925584</v>
+        <v>6925267</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848584</v>
+        <v>124848548</v>
       </c>
       <c r="B5" t="n">
-        <v>88359</v>
+        <v>91166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>456896</v>
+        <v>457064</v>
       </c>
       <c r="R5" t="n">
-        <v>6925616</v>
+        <v>6925274</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848555</v>
+        <v>124848549</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91166</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457075</v>
+        <v>457151</v>
       </c>
       <c r="R6" t="n">
-        <v>6925276</v>
+        <v>6925474</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848546</v>
+        <v>124848576</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>91162</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457165</v>
+        <v>457051</v>
       </c>
       <c r="R7" t="n">
-        <v>6925267</v>
+        <v>6925537</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,6 +1274,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1292,10 +1293,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848560</v>
+        <v>124848551</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,10 +1333,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457173</v>
+        <v>457116</v>
       </c>
       <c r="R8" t="n">
-        <v>6925356</v>
+        <v>6925215</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1400,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848551</v>
+        <v>124848556</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457116</v>
+        <v>456917</v>
       </c>
       <c r="R9" t="n">
-        <v>6925215</v>
+        <v>6925573</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,7 +1480,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska på tall</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848545</v>
+        <v>124848578</v>
       </c>
       <c r="B10" t="n">
-        <v>78905</v>
+        <v>91162</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1523,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>967</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456823</v>
+        <v>456928</v>
       </c>
       <c r="R10" t="n">
-        <v>6925376</v>
+        <v>6925545</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848573</v>
+        <v>124848547</v>
       </c>
       <c r="B11" t="n">
-        <v>78889</v>
+        <v>91166</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1625,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457004</v>
+        <v>456911</v>
       </c>
       <c r="R11" t="n">
-        <v>6925576</v>
+        <v>6925161</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1711,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848553</v>
+        <v>124848545</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>79042</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1727,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>967</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1751,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456909</v>
+        <v>456823</v>
       </c>
       <c r="R12" t="n">
-        <v>6925153</v>
+        <v>6925376</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1786,11 +1787,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,10 +1813,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848547</v>
+        <v>124848557</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,21 +1829,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>456911</v>
+        <v>457156</v>
       </c>
       <c r="R13" t="n">
-        <v>6925161</v>
+        <v>6925470</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,6 +1889,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1919,10 +1920,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848578</v>
+        <v>124848583</v>
       </c>
       <c r="B14" t="n">
-        <v>91008</v>
+        <v>88512</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1936,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1960,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456928</v>
+        <v>456916</v>
       </c>
       <c r="R14" t="n">
-        <v>6925545</v>
+        <v>6925584</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,10 +2022,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848558</v>
+        <v>124848573</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>79026</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2038,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2062,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457197</v>
+        <v>457004</v>
       </c>
       <c r="R15" t="n">
-        <v>6925420</v>
+        <v>6925576</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,11 +2098,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,10 +2124,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848576</v>
+        <v>124848555</v>
       </c>
       <c r="B16" t="n">
-        <v>91008</v>
+        <v>57635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2140,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457051</v>
+        <v>457075</v>
       </c>
       <c r="R16" t="n">
-        <v>6925537</v>
+        <v>6925276</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,13 +2202,17 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2231,10 +2231,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124848557</v>
+        <v>124848554</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457156</v>
+        <v>456857</v>
       </c>
       <c r="R17" t="n">
-        <v>6925470</v>
+        <v>6925333</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2338,10 +2338,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124848556</v>
+        <v>124848560</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>456917</v>
+        <v>457173</v>
       </c>
       <c r="R18" t="n">
-        <v>6925573</v>
+        <v>6925356</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2445,10 +2445,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124848579</v>
+        <v>124848553</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57635</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2461,21 +2461,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456957</v>
+        <v>456909</v>
       </c>
       <c r="R19" t="n">
-        <v>6925524</v>
+        <v>6925153</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2552,10 +2552,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124848554</v>
+        <v>124848558</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>456857</v>
+        <v>457197</v>
       </c>
       <c r="R20" t="n">
-        <v>6925333</v>
+        <v>6925420</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124848549</v>
+        <v>124848577</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
+        <v>91162</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,21 +2675,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457151</v>
+        <v>457050</v>
       </c>
       <c r="R21" t="n">
-        <v>6925474</v>
+        <v>6925282</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -2552,10 +2552,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124848558</v>
+        <v>124848577</v>
       </c>
       <c r="B20" t="n">
-        <v>57635</v>
+        <v>91162</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2592,10 +2592,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457197</v>
+        <v>457050</v>
       </c>
       <c r="R20" t="n">
-        <v>6925420</v>
+        <v>6925282</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,11 +2628,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2659,10 +2654,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124848577</v>
+        <v>124848558</v>
       </c>
       <c r="B21" t="n">
-        <v>91162</v>
+        <v>57635</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2675,21 +2670,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2699,10 +2694,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>457050</v>
+        <v>457197</v>
       </c>
       <c r="R21" t="n">
-        <v>6925282</v>
+        <v>6925420</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2735,6 +2730,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124848579</v>
+        <v>124848584</v>
       </c>
       <c r="B2" t="n">
-        <v>78947</v>
+        <v>88512</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456957</v>
+        <v>456896</v>
       </c>
       <c r="R2" t="n">
-        <v>6925524</v>
+        <v>6925616</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124848584</v>
+        <v>124848555</v>
       </c>
       <c r="B3" t="n">
-        <v>88512</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>456896</v>
+        <v>457075</v>
       </c>
       <c r="R3" t="n">
-        <v>6925616</v>
+        <v>6925276</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124848548</v>
+        <v>124848579</v>
       </c>
       <c r="B5" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457064</v>
+        <v>456957</v>
       </c>
       <c r="R5" t="n">
-        <v>6925274</v>
+        <v>6925524</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124848549</v>
+        <v>124848578</v>
       </c>
       <c r="B6" t="n">
-        <v>91166</v>
+        <v>91162</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457151</v>
+        <v>456928</v>
       </c>
       <c r="R6" t="n">
-        <v>6925474</v>
+        <v>6925545</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124848576</v>
+        <v>124848577</v>
       </c>
       <c r="B7" t="n">
         <v>91162</v>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457051</v>
+        <v>457050</v>
       </c>
       <c r="R7" t="n">
-        <v>6925537</v>
+        <v>6925282</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1274,7 +1279,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1293,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124848551</v>
+        <v>124848547</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1333,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457116</v>
+        <v>456911</v>
       </c>
       <c r="R8" t="n">
-        <v>6925215</v>
+        <v>6925161</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1369,11 +1373,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124848556</v>
+        <v>124848576</v>
       </c>
       <c r="B9" t="n">
-        <v>57635</v>
+        <v>91162</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1440,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>456917</v>
+        <v>457051</v>
       </c>
       <c r="R9" t="n">
-        <v>6925573</v>
+        <v>6925537</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1478,17 +1477,13 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1507,10 +1502,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124848578</v>
+        <v>124848560</v>
       </c>
       <c r="B10" t="n">
-        <v>91162</v>
+        <v>57635</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,21 +1518,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>456928</v>
+        <v>457173</v>
       </c>
       <c r="R10" t="n">
-        <v>6925545</v>
+        <v>6925356</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1583,6 +1578,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1609,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124848547</v>
+        <v>124848554</v>
       </c>
       <c r="B11" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,21 +1625,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1649,10 +1649,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>456911</v>
+        <v>456857</v>
       </c>
       <c r="R11" t="n">
-        <v>6925161</v>
+        <v>6925333</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1685,6 +1685,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1711,10 +1716,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124848545</v>
+        <v>124848556</v>
       </c>
       <c r="B12" t="n">
-        <v>79042</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,21 +1732,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>967</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1751,10 +1756,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>456823</v>
+        <v>456917</v>
       </c>
       <c r="R12" t="n">
-        <v>6925376</v>
+        <v>6925573</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,6 +1792,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1813,10 +1823,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124848557</v>
+        <v>124848583</v>
       </c>
       <c r="B13" t="n">
-        <v>57635</v>
+        <v>88512</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,21 +1839,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1863,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457156</v>
+        <v>456916</v>
       </c>
       <c r="R13" t="n">
-        <v>6925470</v>
+        <v>6925584</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1889,11 +1899,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1920,10 +1925,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124848583</v>
+        <v>124848557</v>
       </c>
       <c r="B14" t="n">
-        <v>88512</v>
+        <v>57635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,21 +1941,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1960,10 +1965,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>456916</v>
+        <v>457156</v>
       </c>
       <c r="R14" t="n">
-        <v>6925584</v>
+        <v>6925470</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1996,6 +2001,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2022,10 +2032,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124848573</v>
+        <v>124848548</v>
       </c>
       <c r="B15" t="n">
-        <v>79026</v>
+        <v>91166</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2038,21 +2048,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>864</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2062,10 +2072,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457004</v>
+        <v>457064</v>
       </c>
       <c r="R15" t="n">
-        <v>6925576</v>
+        <v>6925274</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2124,10 +2134,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124848555</v>
+        <v>124848549</v>
       </c>
       <c r="B16" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2140,21 +2150,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2164,10 +2174,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457075</v>
+        <v>457151</v>
       </c>
       <c r="R16" t="n">
-        <v>6925276</v>
+        <v>6925474</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,11 +2210,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2231,10 +2236,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124848554</v>
+        <v>124848573</v>
       </c>
       <c r="B17" t="n">
-        <v>57635</v>
+        <v>79026</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2247,21 +2252,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2271,10 +2276,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>456857</v>
+        <v>457004</v>
       </c>
       <c r="R17" t="n">
-        <v>6925333</v>
+        <v>6925576</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,11 +2312,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2338,10 +2338,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124848560</v>
+        <v>124848545</v>
       </c>
       <c r="B18" t="n">
-        <v>57635</v>
+        <v>79042</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2354,21 +2354,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>967</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457173</v>
+        <v>456823</v>
       </c>
       <c r="R18" t="n">
-        <v>6925356</v>
+        <v>6925376</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,11 +2414,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2445,7 +2440,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124848553</v>
+        <v>124848551</v>
       </c>
       <c r="B19" t="n">
         <v>57635</v>
@@ -2485,10 +2480,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>456909</v>
+        <v>457116</v>
       </c>
       <c r="R19" t="n">
-        <v>6925153</v>
+        <v>6925215</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2525,7 +2520,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre på tall</t>
+          <t>Ringhack färska på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2552,10 +2547,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124848577</v>
+        <v>124848553</v>
       </c>
       <c r="B20" t="n">
-        <v>91162</v>
+        <v>57635</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2568,21 +2563,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2592,10 +2587,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>457050</v>
+        <v>456909</v>
       </c>
       <c r="R20" t="n">
-        <v>6925282</v>
+        <v>6925153</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2628,6 +2623,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124848558</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>124848560</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>124848556</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>124848555</v>
       </c>
       <c r="B11" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>124848557</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>124848551</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>124848553</v>
       </c>
       <c r="B20" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>124848554</v>
       </c>
       <c r="B21" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124848558</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>124848560</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>124848556</v>
       </c>
       <c r="B7" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>124848555</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>124848557</v>
       </c>
       <c r="B13" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>124848551</v>
       </c>
       <c r="B16" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>124848553</v>
       </c>
       <c r="B20" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>124848554</v>
       </c>
       <c r="B21" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 12459-2025 artfynd.xlsx
+++ b/artfynd/A 12459-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124848558</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>124848560</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>124848556</v>
       </c>
       <c r="B7" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>124848555</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>124848557</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>124848551</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>124848553</v>
       </c>
       <c r="B20" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>124848554</v>
       </c>
       <c r="B21" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
